--- a/缓存数据/enterpriseAndFrame_csm.xlsx
+++ b/缓存数据/enterpriseAndFrame_csm.xlsx
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3739485.060000001</v>
+        <v>2943806.940000002</v>
       </c>
       <c r="C2" t="n">
-        <v>3256969.210000001</v>
+        <v>2438696.420000004</v>
       </c>
       <c r="D2" t="n">
-        <v>482515.8500000001</v>
+        <v>505110.5199999998</v>
       </c>
       <c r="E2" t="n">
-        <v>950868.7500000003</v>
+        <v>966468.8399999995</v>
       </c>
       <c r="F2" t="n">
-        <v>2788616.309999997</v>
+        <v>1977338.099999997</v>
       </c>
     </row>
     <row r="3">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2943806.940000003</v>
+        <v>2958755.649999985</v>
       </c>
       <c r="C3" t="n">
-        <v>2438696.420000004</v>
+        <v>2388765.220000001</v>
       </c>
       <c r="D3" t="n">
-        <v>505110.52</v>
+        <v>569990.4300000002</v>
       </c>
       <c r="E3" t="n">
-        <v>966468.84</v>
+        <v>978632.0200000004</v>
       </c>
       <c r="F3" t="n">
-        <v>1977338.100000003</v>
+        <v>1980123.630000005</v>
       </c>
     </row>
     <row r="4">
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2958755.649999986</v>
+        <v>2919122.259999999</v>
       </c>
       <c r="C4" t="n">
-        <v>2388765.219999994</v>
+        <v>2334468.090000002</v>
       </c>
       <c r="D4" t="n">
-        <v>569990.4299999997</v>
+        <v>584654.1699999995</v>
       </c>
       <c r="E4" t="n">
-        <v>978632.0199999999</v>
+        <v>1000657.57</v>
       </c>
       <c r="F4" t="n">
-        <v>1980123.630000005</v>
+        <v>1918464.690000002</v>
       </c>
     </row>
     <row r="5">
@@ -528,19 +528,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2919122.260000003</v>
+        <v>2935288.850000006</v>
       </c>
       <c r="C5" t="n">
-        <v>2334468.09</v>
+        <v>2418080.750000003</v>
       </c>
       <c r="D5" t="n">
-        <v>584654.1699999993</v>
+        <v>517208.0999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1000657.57</v>
+        <v>990353.1700000003</v>
       </c>
       <c r="F5" t="n">
-        <v>1918464.690000005</v>
+        <v>1944935.68</v>
       </c>
     </row>
     <row r="6">
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2935288.850000001</v>
+        <v>3082568.520000008</v>
       </c>
       <c r="C6" t="n">
-        <v>2418080.750000002</v>
+        <v>2599369.190000001</v>
       </c>
       <c r="D6" t="n">
-        <v>517208.0999999999</v>
+        <v>483199.33</v>
       </c>
       <c r="E6" t="n">
-        <v>990353.1699999999</v>
+        <v>957337.0400000005</v>
       </c>
       <c r="F6" t="n">
-        <v>1944935.68</v>
+        <v>2125231.479999998</v>
       </c>
     </row>
     <row r="7">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3082568.520000006</v>
+        <v>2996307.269999998</v>
       </c>
       <c r="C7" t="n">
-        <v>2599369.190000004</v>
+        <v>2485871.639999997</v>
       </c>
       <c r="D7" t="n">
-        <v>483199.3300000001</v>
+        <v>510435.6299999998</v>
       </c>
       <c r="E7" t="n">
-        <v>957337.0400000005</v>
+        <v>954895.9300000006</v>
       </c>
       <c r="F7" t="n">
-        <v>2125231.480000001</v>
+        <v>2041411.340000002</v>
       </c>
     </row>
     <row r="8">
@@ -594,19 +594,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2996307.270000004</v>
+        <v>3025130.189999998</v>
       </c>
       <c r="C8" t="n">
-        <v>2485871.639999994</v>
+        <v>2458650.759999998</v>
       </c>
       <c r="D8" t="n">
-        <v>510435.6299999998</v>
+        <v>566479.4300000001</v>
       </c>
       <c r="E8" t="n">
-        <v>954895.9300000004</v>
+        <v>988121.4200000006</v>
       </c>
       <c r="F8" t="n">
-        <v>2041411.340000003</v>
+        <v>2037008.769999998</v>
       </c>
     </row>
     <row r="9">
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3025130.19</v>
+        <v>3139499.819999997</v>
       </c>
       <c r="C9" t="n">
-        <v>2458650.760000005</v>
+        <v>2531142.21</v>
       </c>
       <c r="D9" t="n">
-        <v>566479.4299999998</v>
+        <v>608357.6099999999</v>
       </c>
       <c r="E9" t="n">
-        <v>988121.4200000006</v>
+        <v>1041476.999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>2037008.769999996</v>
+        <v>2098022.820000001</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/enterpriseAndFrame_csm.xlsx
+++ b/缓存数据/enterpriseAndFrame_csm.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2943806.940000002</v>
+        <v>3823223.920000006</v>
       </c>
       <c r="C2" t="n">
-        <v>2438696.420000004</v>
+        <v>3361395.72</v>
       </c>
       <c r="D2" t="n">
-        <v>505110.5199999998</v>
+        <v>461828.2</v>
       </c>
       <c r="E2" t="n">
-        <v>966468.8399999995</v>
+        <v>944928.2500000003</v>
       </c>
       <c r="F2" t="n">
-        <v>1977338.099999997</v>
+        <v>2878295.670000003</v>
       </c>
     </row>
     <row r="3">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2958755.649999985</v>
+        <v>5369668.700000009</v>
       </c>
       <c r="C3" t="n">
-        <v>2388765.220000001</v>
+        <v>4944730.090000012</v>
       </c>
       <c r="D3" t="n">
-        <v>569990.4300000002</v>
+        <v>424938.61</v>
       </c>
       <c r="E3" t="n">
-        <v>978632.0200000004</v>
+        <v>920567.4199999997</v>
       </c>
       <c r="F3" t="n">
-        <v>1980123.630000005</v>
+        <v>4449101.280000015</v>
       </c>
     </row>
     <row r="4">
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2919122.259999999</v>
+        <v>5288636.070000002</v>
       </c>
       <c r="C4" t="n">
-        <v>2334468.090000002</v>
+        <v>4913140.760000002</v>
       </c>
       <c r="D4" t="n">
-        <v>584654.1699999995</v>
+        <v>375495.3099999998</v>
       </c>
       <c r="E4" t="n">
-        <v>1000657.57</v>
+        <v>867443.8799999987</v>
       </c>
       <c r="F4" t="n">
-        <v>1918464.690000002</v>
+        <v>4421192.19</v>
       </c>
     </row>
     <row r="5">
@@ -528,19 +528,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2935288.850000006</v>
+        <v>5032204.149999996</v>
       </c>
       <c r="C5" t="n">
-        <v>2418080.750000003</v>
+        <v>4591935.809999994</v>
       </c>
       <c r="D5" t="n">
-        <v>517208.0999999999</v>
+        <v>440268.3399999993</v>
       </c>
       <c r="E5" t="n">
-        <v>990353.1700000003</v>
+        <v>939994.9899999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1944935.68</v>
+        <v>4092209.159999995</v>
       </c>
     </row>
     <row r="6">
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3082568.520000008</v>
+        <v>5164574.979999989</v>
       </c>
       <c r="C6" t="n">
-        <v>2599369.190000001</v>
+        <v>4681950.579999989</v>
       </c>
       <c r="D6" t="n">
-        <v>483199.33</v>
+        <v>482624.4</v>
       </c>
       <c r="E6" t="n">
-        <v>957337.0400000005</v>
+        <v>1025691.59</v>
       </c>
       <c r="F6" t="n">
-        <v>2125231.479999998</v>
+        <v>4138883.389999991</v>
       </c>
     </row>
     <row r="7">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2996307.269999998</v>
+        <v>3297496.039999994</v>
       </c>
       <c r="C7" t="n">
-        <v>2485871.639999997</v>
+        <v>2888150.819999993</v>
       </c>
       <c r="D7" t="n">
-        <v>510435.6299999998</v>
+        <v>409345.2199999999</v>
       </c>
       <c r="E7" t="n">
-        <v>954895.9300000006</v>
+        <v>932844.0399999997</v>
       </c>
       <c r="F7" t="n">
-        <v>2041411.340000002</v>
+        <v>2364651.999999995</v>
       </c>
     </row>
     <row r="8">
@@ -594,19 +594,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3025130.189999998</v>
+        <v>3181977.089999999</v>
       </c>
       <c r="C8" t="n">
-        <v>2458650.759999998</v>
+        <v>2790315.670000004</v>
       </c>
       <c r="D8" t="n">
-        <v>566479.4300000001</v>
+        <v>391661.42</v>
       </c>
       <c r="E8" t="n">
-        <v>988121.4200000006</v>
+        <v>899937.6900000003</v>
       </c>
       <c r="F8" t="n">
-        <v>2037008.769999998</v>
+        <v>2282039.400000003</v>
       </c>
     </row>
     <row r="9">
@@ -616,22 +616,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3139499.819999997</v>
+        <v>2868250</v>
       </c>
       <c r="C9" t="n">
-        <v>2531142.21</v>
+        <v>2511461.750000005</v>
       </c>
       <c r="D9" t="n">
-        <v>608357.6099999999</v>
+        <v>356788.2500000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1041476.999999999</v>
+        <v>890260.8499999997</v>
       </c>
       <c r="F9" t="n">
-        <v>2098022.820000001</v>
+        <v>1977989.150000003</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>